--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T08:50:20+00:00</t>
+    <t>2023-05-10T08:50:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T08:50:38+00:00</t>
+    <t>2023-05-10T09:16:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:16:32+00:00</t>
+    <t>2023-05-10T09:16:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:16:57+00:00</t>
+    <t>2023-05-10T09:45:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:45:15+00:00</t>
+    <t>2023-05-10T09:50:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:50:54+00:00</t>
+    <t>2023-05-10T10:15:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T10:15:35+00:00</t>
+    <t>2023-05-10T10:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T10:16:16+00:00</t>
+    <t>2023-05-10T11:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:05:21+00:00</t>
+    <t>2023-05-10T11:05:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:05:55+00:00</t>
+    <t>2023-05-10T11:27:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:27:56+00:00</t>
+    <t>2023-05-10T11:35:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:35:39+00:00</t>
+    <t>2023-05-10T12:21:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T12:21:05+00:00</t>
+    <t>2023-05-10T12:21:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T12:21:34+00:00</t>
+    <t>2023-05-11T06:47:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T06:47:47+00:00</t>
+    <t>2023-05-11T06:48:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T06:48:00+00:00</t>
+    <t>2023-05-11T06:54:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T06:54:20+00:00</t>
+    <t>2023-05-11T06:54:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T06:54:25+00:00</t>
+    <t>2023-05-11T08:35:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -536,7 +536,7 @@
     <t>Organizations are known by a variety of ids. Some institutions maintain several, and most collect identifiers for exchange with other organizations concerning the organization.</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:system}
+    <t xml:space="preserve">exists:system}
 </t>
   </si>
   <si>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>89</v>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T08:35:45+00:00</t>
+    <t>2023-05-11T08:41:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T08:41:43+00:00</t>
+    <t>2023-05-11T09:08:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -536,7 +536,7 @@
     <t>Organizations are known by a variety of ids. Some institutions maintain several, and most collect identifiers for exchange with other organizations concerning the organization.</t>
   </si>
   <si>
-    <t xml:space="preserve">exists:system}
+    <t xml:space="preserve">value:system}
 </t>
   </si>
   <si>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>89</v>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T09:08:26+00:00</t>
+    <t>2023-05-11T09:17:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T09:17:12+00:00</t>
+    <t>2023-05-11T10:17:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:17:25+00:00</t>
+    <t>2023-05-11T10:17:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:17:56+00:00</t>
+    <t>2023-05-11T10:34:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:34:10+00:00</t>
+    <t>2023-05-11T10:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2595" uniqueCount="545">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2595" uniqueCount="544">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:41:58+00:00</t>
+    <t>2023-05-11T10:56:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -541,9 +541,6 @@
   </si>
   <si>
     <t>Slice based on the type of identifier.</t>
-  </si>
-  <si>
-    <t>openAtEnd</t>
   </si>
   <si>
     <t xml:space="preserve">org-1
@@ -3564,7 +3561,7 @@
         <v>78</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>168</v>
+        <v>141</v>
       </c>
       <c r="AF13" t="s" s="2">
         <v>161</v>
@@ -3576,36 +3573,36 @@
         <v>80</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AL13" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="AL13" t="s" s="2">
+      <c r="AM13" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="AM13" t="s" s="2">
+      <c r="AN13" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="AN13" t="s" s="2">
+      <c r="AO13" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="AO13" t="s" s="2">
-        <v>174</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>161</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>78</v>
@@ -3695,33 +3692,33 @@
         <v>80</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AL14" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="AL14" t="s" s="2">
+      <c r="AM14" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="AM14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="AN14" t="s" s="2">
+      <c r="AO14" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>174</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3747,10 +3744,10 @@
         <v>91</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3801,7 +3798,7 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3810,19 +3807,19 @@
         <v>89</v>
       </c>
       <c r="AI15" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM15" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="AJ15" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK15" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>78</v>
@@ -3833,10 +3830,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3862,10 +3859,10 @@
         <v>137</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>158</v>
@@ -3909,7 +3906,7 @@
         <v>140</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>78</v>
@@ -3918,7 +3915,7 @@
         <v>141</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3939,7 +3936,7 @@
         <v>78</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>78</v>
@@ -3950,10 +3947,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3979,16 +3976,16 @@
         <v>109</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>78</v>
@@ -4016,28 +4013,28 @@
         <v>113</v>
       </c>
       <c r="Y17" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="Z17" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="Z17" t="s" s="2">
+      <c r="AA17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -4058,7 +4055,7 @@
         <v>134</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>78</v>
@@ -4069,10 +4066,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4095,19 +4092,19 @@
         <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>78</v>
@@ -4132,31 +4129,31 @@
         <v>78</v>
       </c>
       <c r="X18" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="Y18" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="Y18" t="s" s="2">
+      <c r="Z18" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="Z18" t="s" s="2">
+      <c r="AA18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF18" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="AA18" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB18" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD18" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE18" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -4174,10 +4171,10 @@
         <v>78</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>78</v>
@@ -4188,10 +4185,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4217,10 +4214,10 @@
         <v>91</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4271,7 +4268,7 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4280,19 +4277,19 @@
         <v>89</v>
       </c>
       <c r="AI19" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM19" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="AJ19" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK19" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>78</v>
@@ -4303,10 +4300,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4332,10 +4329,10 @@
         <v>137</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>158</v>
@@ -4379,7 +4376,7 @@
         <v>140</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>78</v>
@@ -4388,7 +4385,7 @@
         <v>141</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -4409,7 +4406,7 @@
         <v>78</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>78</v>
@@ -4420,10 +4417,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4446,19 +4443,19 @@
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="N21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>78</v>
@@ -4507,7 +4504,7 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4525,10 +4522,10 @@
         <v>78</v>
       </c>
       <c r="AL21" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>78</v>
@@ -4539,10 +4536,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="B22" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4568,10 +4565,10 @@
         <v>91</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4622,7 +4619,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4631,19 +4628,19 @@
         <v>89</v>
       </c>
       <c r="AI22" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="AJ22" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK22" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL22" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>78</v>
@@ -4654,10 +4651,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="B23" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4683,10 +4680,10 @@
         <v>137</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="N23" t="s" s="2">
         <v>158</v>
@@ -4730,7 +4727,7 @@
         <v>140</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>78</v>
@@ -4739,7 +4736,7 @@
         <v>141</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4760,7 +4757,7 @@
         <v>78</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>78</v>
@@ -4771,10 +4768,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="B24" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>231</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4800,16 +4797,16 @@
         <v>103</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>78</v>
@@ -4819,46 +4816,46 @@
         <v>78</v>
       </c>
       <c r="S24" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="T24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF24" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="T24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4876,10 +4873,10 @@
         <v>78</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>78</v>
@@ -4890,10 +4887,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="B25" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4916,16 +4913,16 @@
         <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4975,7 +4972,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4993,10 +4990,10 @@
         <v>78</v>
       </c>
       <c r="AL25" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>78</v>
@@ -5007,10 +5004,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5036,14 +5033,14 @@
         <v>109</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>78</v>
@@ -5053,46 +5050,46 @@
         <v>78</v>
       </c>
       <c r="S26" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="T26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="T26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -5101,7 +5098,7 @@
         <v>89</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>101</v>
@@ -5110,10 +5107,10 @@
         <v>78</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>78</v>
@@ -5124,10 +5121,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5150,17 +5147,17 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>78</v>
@@ -5170,46 +5167,46 @@
         <v>78</v>
       </c>
       <c r="S27" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="T27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -5218,7 +5215,7 @@
         <v>89</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>101</v>
@@ -5227,10 +5224,10 @@
         <v>78</v>
       </c>
       <c r="AL27" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>78</v>
@@ -5241,10 +5238,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5267,19 +5264,19 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="N28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>78</v>
@@ -5328,7 +5325,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5346,10 +5343,10 @@
         <v>78</v>
       </c>
       <c r="AL28" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>78</v>
@@ -5360,10 +5357,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5386,19 +5383,19 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>78</v>
@@ -5408,46 +5405,46 @@
         <v>78</v>
       </c>
       <c r="S29" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="T29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5465,10 +5462,10 @@
         <v>78</v>
       </c>
       <c r="AL29" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>78</v>
@@ -5479,10 +5476,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="B30" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5508,65 +5505,65 @@
         <v>103</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="N30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T30" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="S30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T30" t="s" s="2">
+      <c r="U30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF30" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="U30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5584,24 +5581,24 @@
         <v>78</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO30" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>299</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5624,16 +5621,16 @@
         <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5647,43 +5644,43 @@
         <v>78</v>
       </c>
       <c r="T31" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF31" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="U31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5692,7 +5689,7 @@
         <v>89</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>101</v>
@@ -5701,24 +5698,24 @@
         <v>78</v>
       </c>
       <c r="AL31" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="AM31" t="s" s="2">
+      <c r="AN31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO31" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>310</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="B32" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5741,13 +5738,13 @@
         <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5798,7 +5795,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5816,24 +5813,24 @@
         <v>78</v>
       </c>
       <c r="AL32" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="AM32" t="s" s="2">
+      <c r="AN32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO32" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>319</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="B33" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5856,16 +5853,16 @@
         <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5915,7 +5912,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5933,24 +5930,24 @@
         <v>78</v>
       </c>
       <c r="AL33" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO33" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>329</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5973,26 +5970,26 @@
         <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="N34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="O34" t="s" s="2">
+      <c r="P34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q34" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="P34" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q34" t="s" s="2">
-        <v>335</v>
-      </c>
       <c r="R34" t="s" s="2">
         <v>78</v>
       </c>
@@ -6036,7 +6033,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -6051,27 +6048,27 @@
         <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AL34" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="AL34" t="s" s="2">
+      <c r="AM34" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="AM34" t="s" s="2">
+      <c r="AN34" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>340</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6094,19 +6091,19 @@
         <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>78</v>
@@ -6131,14 +6128,14 @@
         <v>78</v>
       </c>
       <c r="X35" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="Y35" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="Y35" t="s" s="2">
+      <c r="Z35" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="Z35" t="s" s="2">
-        <v>348</v>
-      </c>
       <c r="AA35" t="s" s="2">
         <v>78</v>
       </c>
@@ -6155,7 +6152,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6170,27 +6167,27 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AL35" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AL35" t="s" s="2">
+      <c r="AM35" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="AM35" t="s" s="2">
-        <v>351</v>
-      </c>
       <c r="AN35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6213,19 +6210,19 @@
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -6274,7 +6271,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6283,7 +6280,7 @@
         <v>89</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>101</v>
@@ -6292,24 +6289,24 @@
         <v>78</v>
       </c>
       <c r="AL36" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AM36" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AM36" t="s" s="2">
+      <c r="AN36" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="AN36" t="s" s="2">
+      <c r="AO36" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>360</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6332,19 +6329,19 @@
         <v>78</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>78</v>
@@ -6393,7 +6390,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6414,7 +6411,7 @@
         <v>78</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>78</v>
@@ -6425,10 +6422,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6451,17 +6448,17 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>78</v>
@@ -6510,7 +6507,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6531,7 +6528,7 @@
         <v>78</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>78</v>
@@ -6542,10 +6539,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6568,19 +6565,19 @@
         <v>78</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>78</v>
@@ -6629,7 +6626,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6641,16 +6638,16 @@
         <v>78</v>
       </c>
       <c r="AJ39" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="AK39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>78</v>
@@ -6661,10 +6658,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6690,10 +6687,10 @@
         <v>91</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6744,7 +6741,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6753,19 +6750,19 @@
         <v>89</v>
       </c>
       <c r="AI40" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>78</v>
@@ -6776,10 +6773,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6805,10 +6802,10 @@
         <v>137</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>158</v>
@@ -6852,7 +6849,7 @@
         <v>140</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>78</v>
@@ -6861,7 +6858,7 @@
         <v>141</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6882,7 +6879,7 @@
         <v>78</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>78</v>
@@ -6893,10 +6890,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6919,16 +6916,16 @@
         <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6954,31 +6951,31 @@
         <v>78</v>
       </c>
       <c r="X42" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="Y42" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="Y42" t="s" s="2">
+      <c r="Z42" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="Z42" t="s" s="2">
+      <c r="AA42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF42" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="AA42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7010,10 +7007,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7036,16 +7033,16 @@
         <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7095,7 +7092,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7127,10 +7124,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7153,13 +7150,13 @@
         <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7210,7 +7207,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7242,10 +7239,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7268,16 +7265,16 @@
         <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7327,7 +7324,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7359,10 +7356,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7388,10 +7385,10 @@
         <v>91</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7442,7 +7439,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7451,19 +7448,19 @@
         <v>89</v>
       </c>
       <c r="AI46" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="AJ46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>78</v>
@@ -7474,10 +7471,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7503,10 +7500,10 @@
         <v>137</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>158</v>
@@ -7550,7 +7547,7 @@
         <v>140</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>78</v>
@@ -7559,7 +7556,7 @@
         <v>141</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7580,7 +7577,7 @@
         <v>78</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>78</v>
@@ -7591,10 +7588,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7620,16 +7617,16 @@
         <v>109</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>78</v>
@@ -7642,7 +7639,7 @@
         <v>78</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="U48" t="s" s="2">
         <v>78</v>
@@ -7657,28 +7654,28 @@
         <v>113</v>
       </c>
       <c r="Y48" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="Z48" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="Z48" t="s" s="2">
+      <c r="AA48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF48" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7696,24 +7693,24 @@
         <v>78</v>
       </c>
       <c r="AL48" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AM48" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AM48" t="s" s="2">
+      <c r="AN48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO48" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>420</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7739,13 +7736,13 @@
         <v>109</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7759,7 +7756,7 @@
         <v>78</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="U49" t="s" s="2">
         <v>78</v>
@@ -7774,28 +7771,28 @@
         <v>113</v>
       </c>
       <c r="Y49" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="Z49" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="Z49" t="s" s="2">
+      <c r="AA49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF49" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7813,10 +7810,10 @@
         <v>78</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>78</v>
@@ -7827,10 +7824,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7853,19 +7850,19 @@
         <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>78</v>
@@ -7878,43 +7875,43 @@
         <v>78</v>
       </c>
       <c r="T50" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF50" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="U50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7932,10 +7929,10 @@
         <v>78</v>
       </c>
       <c r="AL50" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AM50" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>78</v>
@@ -7946,10 +7943,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7972,13 +7969,13 @@
         <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7993,43 +7990,43 @@
         <v>78</v>
       </c>
       <c r="T51" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF51" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="U51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8047,28 +8044,28 @@
         <v>78</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="AM51" t="s" s="2">
+      <c r="AN51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO51" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>446</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8087,13 +8084,13 @@
         <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8108,43 +8105,43 @@
         <v>78</v>
       </c>
       <c r="T52" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF52" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="U52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8162,28 +8159,28 @@
         <v>78</v>
       </c>
       <c r="AL52" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AM52" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="AM52" t="s" s="2">
+      <c r="AN52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO52" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>455</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8202,16 +8199,16 @@
         <v>90</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8225,43 +8222,43 @@
         <v>78</v>
       </c>
       <c r="T53" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF53" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="U53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8279,10 +8276,10 @@
         <v>78</v>
       </c>
       <c r="AL53" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AM53" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>78</v>
@@ -8293,14 +8290,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8319,13 +8316,13 @@
         <v>90</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8376,7 +8373,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8394,28 +8391,28 @@
         <v>78</v>
       </c>
       <c r="AL54" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="AM54" t="s" s="2">
+      <c r="AN54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO54" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>472</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8434,13 +8431,13 @@
         <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8455,43 +8452,43 @@
         <v>78</v>
       </c>
       <c r="T55" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF55" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="U55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8509,24 +8506,24 @@
         <v>78</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="AM55" t="s" s="2">
+      <c r="AN55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO55" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>481</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8549,16 +8546,16 @@
         <v>90</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8608,7 +8605,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8626,24 +8623,24 @@
         <v>78</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="AM56" t="s" s="2">
+      <c r="AN56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO56" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>489</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8666,17 +8663,17 @@
         <v>90</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>78</v>
@@ -8689,43 +8686,43 @@
         <v>78</v>
       </c>
       <c r="T57" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF57" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="U57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8743,24 +8740,24 @@
         <v>78</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="AM57" t="s" s="2">
-        <v>497</v>
-      </c>
       <c r="AN57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8783,17 +8780,17 @@
         <v>90</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>500</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>78</v>
@@ -8842,7 +8839,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8874,10 +8871,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8900,16 +8897,16 @@
         <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8959,7 +8956,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8991,10 +8988,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9017,17 +9014,17 @@
         <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>78</v>
@@ -9076,7 +9073,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9094,24 +9091,24 @@
         <v>78</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9134,17 +9131,17 @@
         <v>78</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>78</v>
@@ -9193,7 +9190,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9214,7 +9211,7 @@
         <v>78</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>78</v>
@@ -9225,10 +9222,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9251,13 +9248,13 @@
         <v>78</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>520</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>521</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9308,7 +9305,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9326,10 +9323,10 @@
         <v>78</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>78</v>
@@ -9340,10 +9337,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9366,13 +9363,13 @@
         <v>78</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9423,7 +9420,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9432,19 +9429,19 @@
         <v>89</v>
       </c>
       <c r="AI63" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM63" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>78</v>
@@ -9455,10 +9452,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9484,10 +9481,10 @@
         <v>137</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>158</v>
@@ -9540,7 +9537,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9561,7 +9558,7 @@
         <v>78</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>78</v>
@@ -9572,14 +9569,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9601,10 +9598,10 @@
         <v>137</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>158</v>
@@ -9659,7 +9656,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9691,10 +9688,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9720,14 +9717,14 @@
         <v>162</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>531</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>532</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>78</v>
@@ -9776,7 +9773,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9797,7 +9794,7 @@
         <v>78</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>78</v>
@@ -9808,10 +9805,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9834,13 +9831,13 @@
         <v>78</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>536</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9867,10 +9864,10 @@
         <v>78</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="Z67" t="s" s="2">
         <v>78</v>
@@ -9891,7 +9888,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>89</v>
@@ -9912,7 +9909,7 @@
         <v>78</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>78</v>
@@ -9923,10 +9920,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9949,17 +9946,17 @@
         <v>78</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>78</v>
@@ -10008,7 +10005,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10029,7 +10026,7 @@
         <v>78</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>78</v>
@@ -10040,10 +10037,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10066,13 +10063,13 @@
         <v>78</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10123,7 +10120,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10144,7 +10141,7 @@
         <v>78</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>78</v>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:56:16+00:00</t>
+    <t>2023-05-11T10:56:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:56:44+00:00</t>
+    <t>2023-05-11T11:14:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T11:14:34+00:00</t>
+    <t>2023-05-11T11:21:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/performing-organization</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/StructureDefinition/performing-organization</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T11:21:30+00:00</t>
+    <t>2023-05-11T11:55:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -471,7 +471,7 @@
     <t>ProvinceIndex</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/StructureDefinition/performing-organization-province-index}
+    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/StructureDefinition/performing-organization-province-index}
 </t>
   </si>
   <si>
@@ -487,7 +487,7 @@
     <t>DistrictIndex</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/StructureDefinition/performing-organization-district-index}
+    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/StructureDefinition/performing-organization-district-index}
 </t>
   </si>
   <si>
@@ -2039,7 +2039,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="99.38671875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="146.66796875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T11:55:17+00:00</t>
+    <t>2023-05-11T12:03:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/StructureDefinition/performing-organization</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/performing-organization</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:03:20+00:00</t>
+    <t>2023-05-11T12:08:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -471,7 +471,7 @@
     <t>ProvinceIndex</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/StructureDefinition/performing-organization-province-index}
+    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/StructureDefinition/performing-organization-province-index}
 </t>
   </si>
   <si>
@@ -487,7 +487,7 @@
     <t>DistrictIndex</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/StructureDefinition/performing-organization-district-index}
+    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/StructureDefinition/performing-organization-district-index}
 </t>
   </si>
   <si>
@@ -2039,7 +2039,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="146.66796875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="99.38671875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:08:48+00:00</t>
+    <t>2023-05-11T12:16:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:16:35+00:00</t>
+    <t>2023-05-11T12:20:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:20:22+00:00</t>
+    <t>2023-05-11T12:21:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:21:18+00:00</t>
+    <t>2023-05-11T15:25:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T15:25:42+00:00</t>
+    <t>2023-05-11T15:26:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T15:26:02+00:00</t>
+    <t>2023-05-11T16:43:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:43:02+00:00</t>
+    <t>2023-05-11T16:43:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:43:55+00:00</t>
+    <t>2023-05-11T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:57:46+00:00</t>
+    <t>2023-05-11T16:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:58:30+00:00</t>
+    <t>2023-05-11T17:51:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T17:51:02+00:00</t>
+    <t>2023-05-11T17:51:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/performing-organization</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/StructureDefinition/performing-organization</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T17:51:30+00:00</t>
+    <t>2023-05-11T18:15:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -471,7 +471,7 @@
     <t>ProvinceIndex</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/StructureDefinition/performing-organization-province-index}
+    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/StructureDefinition/performing-organization-province-index}
 </t>
   </si>
   <si>
@@ -487,7 +487,7 @@
     <t>DistrictIndex</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/StructureDefinition/performing-organization-district-index}
+    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/StructureDefinition/performing-organization-district-index}
 </t>
   </si>
   <si>
@@ -2039,7 +2039,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="99.38671875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="142.33984375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:15:51+00:00</t>
+    <t>2023-05-11T18:16:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/StructureDefinition/performing-organization</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/performing-organization</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:16:31+00:00</t>
+    <t>2023-05-11T18:27:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -471,7 +471,7 @@
     <t>ProvinceIndex</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/StructureDefinition/performing-organization-province-index}
+    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/StructureDefinition/performing-organization-province-index}
 </t>
   </si>
   <si>
@@ -487,7 +487,7 @@
     <t>DistrictIndex</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/StructureDefinition/performing-organization-district-index}
+    <t xml:space="preserve">Extension {http://openhie.org/fhir/rwanda-hiv/StructureDefinition/performing-organization-district-index}
 </t>
   </si>
   <si>
@@ -2039,7 +2039,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="142.33984375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="99.38671875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:27:59+00:00</t>
+    <t>2023-05-11T18:29:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:29:46+00:00</t>
+    <t>2023-05-11T18:48:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:48:31+00:00</t>
+    <t>2023-05-11T18:54:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:54:41+00:00</t>
+    <t>2023-05-11T19:41:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:41:30+00:00</t>
+    <t>2023-05-11T19:42:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:42:15+00:00</t>
+    <t>2023-05-11T20:23:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:23:29+00:00</t>
+    <t>2023-05-11T20:24:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:24:51+00:00</t>
+    <t>2023-05-12T02:48:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T02:48:54+00:00</t>
+    <t>2023-05-12T02:49:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T02:49:37+00:00</t>
+    <t>2023-05-12T07:30:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:30:25+00:00</t>
+    <t>2023-05-12T07:30:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:30:35+00:00</t>
+    <t>2023-05-12T07:36:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:36:14+00:00</t>
+    <t>2023-05-12T07:36:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:36:30+00:00</t>
+    <t>2023-05-12T07:54:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:54:06+00:00</t>
+    <t>2023-05-12T07:55:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:55:51+00:00</t>
+    <t>2023-05-12T10:26:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:26:59+00:00</t>
+    <t>2023-05-12T10:27:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:27:50+00:00</t>
+    <t>2023-05-12T10:32:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:32:06+00:00</t>
+    <t>2023-05-12T10:40:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:40:31+00:00</t>
+    <t>2023-05-12T13:37:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:37:18+00:00</t>
+    <t>2023-05-12T13:51:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:51:30+00:00</t>
+    <t>2023-05-23T09:07:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
+++ b/branches/Richard-FHIR-R5/StructureDefinition-performing-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-23T09:07:38+00:00</t>
+    <t>2023-05-23T09:13:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
